--- a/Employee_Reports_wi48/Crisfo Lo Nibal Q0489.xlsx
+++ b/Employee_Reports_wi48/Crisfo Lo Nibal Q0489.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1558,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1754,11 +1754,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1803,11 +1803,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1852,11 +1852,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1901,11 +1901,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1950,11 +1950,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1999,11 +1999,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2048,11 +2048,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2097,11 +2097,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2195,11 +2195,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2244,11 +2244,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2293,11 +2293,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2316,9 +2316,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
           <t>11-Jun-2026</t>
@@ -2330,11 +2342,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2353,9 +2365,21 @@
           <t>Equipment Operation Procedure(QDF-SOP-003) (SOPs)</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>DFWH</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>LSME-QDF-SOP-003</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
           <t>06-Apr-2026</t>
@@ -2367,11 +2391,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2416,11 +2440,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2465,11 +2489,11 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2514,11 +2538,11 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2563,11 +2587,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2612,11 +2636,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2649,11 +2673,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2686,11 +2710,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3148,7 +3172,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7565</v>
+        <v>7562</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
